--- a/转录数据/实验材料1.xlsx
+++ b/转录数据/实验材料1.xlsx
@@ -32,11 +32,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">
@@ -401,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F361"/>
+  <dimension ref="A1:G361"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -422,6 +418,9 @@
       <c r="F1" t="str">
         <v>实验条件</v>
       </c>
+      <c r="G1" t="str">
+        <v>有无生命性</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -442,6 +441,9 @@
       <c r="F2" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G2" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -462,6 +464,9 @@
       <c r="F3" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G3" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -482,6 +487,9 @@
       <c r="F4" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G4" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -502,6 +510,9 @@
       <c r="F5" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G5" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -522,6 +533,9 @@
       <c r="F6" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G6" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -542,6 +556,9 @@
       <c r="F7" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G7" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -562,6 +579,9 @@
       <c r="F8" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G8" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -582,6 +602,9 @@
       <c r="F9" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G9" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -602,6 +625,9 @@
       <c r="F10" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G10" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -622,6 +648,9 @@
       <c r="F11" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G11" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -642,6 +671,9 @@
       <c r="F12" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G12" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -662,6 +694,9 @@
       <c r="F13" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G13" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -682,6 +717,9 @@
       <c r="F14" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G14" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -702,6 +740,9 @@
       <c r="F15" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G15" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -722,6 +763,9 @@
       <c r="F16" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G16" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -742,6 +786,9 @@
       <c r="F17" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G17" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -762,6 +809,9 @@
       <c r="F18" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G18" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -782,6 +832,9 @@
       <c r="F19" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G19" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -802,6 +855,9 @@
       <c r="F20" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G20" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -822,6 +878,9 @@
       <c r="F21" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G21" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -842,6 +901,9 @@
       <c r="F22" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G22" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -862,6 +924,9 @@
       <c r="F23" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G23" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -882,6 +947,9 @@
       <c r="F24" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G24" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -902,6 +970,9 @@
       <c r="F25" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G25" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -922,6 +993,9 @@
       <c r="F26" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G26" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -942,6 +1016,9 @@
       <c r="F27" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G27" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -962,6 +1039,9 @@
       <c r="F28" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G28" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -982,6 +1062,9 @@
       <c r="F29" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G29" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -1002,6 +1085,9 @@
       <c r="F30" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G30" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -1022,6 +1108,9 @@
       <c r="F31" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G31" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -1042,6 +1131,9 @@
       <c r="F32" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G32" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -1062,6 +1154,9 @@
       <c r="F33" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G33" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -1082,6 +1177,9 @@
       <c r="F34" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G34" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -1102,6 +1200,9 @@
       <c r="F35" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G35" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -1122,6 +1223,9 @@
       <c r="F36" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G36" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -1142,6 +1246,9 @@
       <c r="F37" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G37" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -1162,6 +1269,9 @@
       <c r="F38" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G38" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -1182,6 +1292,9 @@
       <c r="F39" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G39" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -1202,6 +1315,9 @@
       <c r="F40" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G40" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -1222,6 +1338,9 @@
       <c r="F41" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G41" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -1242,6 +1361,9 @@
       <c r="F42" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G42" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -1262,6 +1384,9 @@
       <c r="F43" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G43" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -1282,6 +1407,9 @@
       <c r="F44" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G44" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -1302,6 +1430,9 @@
       <c r="F45" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G45" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -1322,6 +1453,9 @@
       <c r="F46" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G46" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -1342,6 +1476,9 @@
       <c r="F47" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G47" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -1362,6 +1499,9 @@
       <c r="F48" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G48" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -1382,6 +1522,9 @@
       <c r="F49" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G49" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -1402,6 +1545,9 @@
       <c r="F50" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G50" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -1422,6 +1568,9 @@
       <c r="F51" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G51" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -1442,6 +1591,9 @@
       <c r="F52" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G52" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -1462,6 +1614,9 @@
       <c r="F53" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G53" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -1482,6 +1637,9 @@
       <c r="F54" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G54" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -1502,6 +1660,9 @@
       <c r="F55" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G55" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -1522,6 +1683,9 @@
       <c r="F56" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G56" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -1542,6 +1706,9 @@
       <c r="F57" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G57" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -1562,6 +1729,9 @@
       <c r="F58" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G58" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -1582,6 +1752,9 @@
       <c r="F59" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G59" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -1602,6 +1775,9 @@
       <c r="F60" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G60" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -1622,6 +1798,9 @@
       <c r="F61" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G61" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -1642,6 +1821,9 @@
       <c r="F62" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G62" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -1662,6 +1844,9 @@
       <c r="F63" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G63" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -1682,6 +1867,9 @@
       <c r="F64" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G64" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -1702,6 +1890,9 @@
       <c r="F65" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G65" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -1722,6 +1913,9 @@
       <c r="F66" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G66" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -1742,6 +1936,9 @@
       <c r="F67" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G67" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -1762,6 +1959,9 @@
       <c r="F68" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G68" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
@@ -1782,6 +1982,9 @@
       <c r="F69" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G69" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
@@ -1802,6 +2005,9 @@
       <c r="F70" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G70" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -1822,6 +2028,9 @@
       <c r="F71" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G71" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -1842,6 +2051,9 @@
       <c r="F72" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G72" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -1862,6 +2074,9 @@
       <c r="F73" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G73" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
@@ -1882,6 +2097,9 @@
       <c r="F74" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G74" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
@@ -1902,6 +2120,9 @@
       <c r="F75" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G75" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -1922,6 +2143,9 @@
       <c r="F76" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G76" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -1942,6 +2166,9 @@
       <c r="F77" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G77" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -1962,6 +2189,9 @@
       <c r="F78" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G78" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -1982,6 +2212,9 @@
       <c r="F79" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G79" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -2002,6 +2235,9 @@
       <c r="F80" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G80" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -2022,6 +2258,9 @@
       <c r="F81" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G81" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
@@ -2042,6 +2281,9 @@
       <c r="F82" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G82" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -2062,6 +2304,9 @@
       <c r="F83" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G83" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -2082,6 +2327,9 @@
       <c r="F84" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G84" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -2102,6 +2350,9 @@
       <c r="F85" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G85" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -2122,6 +2373,9 @@
       <c r="F86" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G86" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
@@ -2142,6 +2396,9 @@
       <c r="F87" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G87" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
@@ -2162,6 +2419,9 @@
       <c r="F88" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G88" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
@@ -2182,6 +2442,9 @@
       <c r="F89" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G89" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
@@ -2202,6 +2465,9 @@
       <c r="F90" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G90" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
@@ -2222,6 +2488,9 @@
       <c r="F91" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G91" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
@@ -2242,6 +2511,9 @@
       <c r="F92" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G92" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -2262,6 +2534,9 @@
       <c r="F93" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G93" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -2282,6 +2557,9 @@
       <c r="F94" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G94" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -2302,6 +2580,9 @@
       <c r="F95" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G95" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
@@ -2322,6 +2603,9 @@
       <c r="F96" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G96" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
@@ -2342,6 +2626,9 @@
       <c r="F97" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G97" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
@@ -2362,6 +2649,9 @@
       <c r="F98" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G98" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -2382,6 +2672,9 @@
       <c r="F99" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G99" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
@@ -2402,6 +2695,9 @@
       <c r="F100" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G100" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
@@ -2422,6 +2718,9 @@
       <c r="F101" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G101" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -2442,6 +2741,9 @@
       <c r="F102" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G102" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
@@ -2462,6 +2764,9 @@
       <c r="F103" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G103" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
@@ -2482,6 +2787,9 @@
       <c r="F104" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G104" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -2502,6 +2810,9 @@
       <c r="F105" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G105" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -2522,6 +2833,9 @@
       <c r="F106" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G106" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -2542,6 +2856,9 @@
       <c r="F107" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G107" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -2562,6 +2879,9 @@
       <c r="F108" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G108" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
@@ -2582,6 +2902,9 @@
       <c r="F109" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G109" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
@@ -2602,6 +2925,9 @@
       <c r="F110" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G110" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
@@ -2622,6 +2948,9 @@
       <c r="F111" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G111" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
@@ -2642,6 +2971,9 @@
       <c r="F112" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G112" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
@@ -2662,6 +2994,9 @@
       <c r="F113" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G113" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -2682,6 +3017,9 @@
       <c r="F114" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G114" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
@@ -2702,6 +3040,9 @@
       <c r="F115" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G115" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
@@ -2722,6 +3063,9 @@
       <c r="F116" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G116" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
@@ -2742,6 +3086,9 @@
       <c r="F117" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G117" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
@@ -2762,6 +3109,9 @@
       <c r="F118" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G118" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
@@ -2782,6 +3132,9 @@
       <c r="F119" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G119" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
@@ -2802,6 +3155,9 @@
       <c r="F120" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G120" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
@@ -2822,6 +3178,9 @@
       <c r="F121" t="str">
         <v>名词任务</v>
       </c>
+      <c r="G121" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
@@ -2842,6 +3201,9 @@
       <c r="F122" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G122" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -2862,6 +3224,9 @@
       <c r="F123" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G123" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -2882,6 +3247,9 @@
       <c r="F124" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G124" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -2902,6 +3270,9 @@
       <c r="F125" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G125" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -2922,6 +3293,9 @@
       <c r="F126" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G126" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
@@ -2942,6 +3316,9 @@
       <c r="F127" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G127" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
@@ -2962,6 +3339,9 @@
       <c r="F128" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G128" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
@@ -2982,6 +3362,9 @@
       <c r="F129" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G129" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
@@ -3002,6 +3385,9 @@
       <c r="F130" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G130" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
@@ -3022,6 +3408,9 @@
       <c r="F131" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G131" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -3042,6 +3431,9 @@
       <c r="F132" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G132" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -3062,6 +3454,9 @@
       <c r="F133" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G133" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -3082,6 +3477,9 @@
       <c r="F134" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G134" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -3102,6 +3500,9 @@
       <c r="F135" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G135" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
@@ -3122,6 +3523,9 @@
       <c r="F136" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G136" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
@@ -3142,6 +3546,9 @@
       <c r="F137" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G137" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
@@ -3162,6 +3569,9 @@
       <c r="F138" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G138" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
@@ -3182,6 +3592,9 @@
       <c r="F139" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G139" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
@@ -3202,6 +3615,9 @@
       <c r="F140" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G140" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
@@ -3222,6 +3638,9 @@
       <c r="F141" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G141" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
@@ -3242,6 +3661,9 @@
       <c r="F142" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G142" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
@@ -3262,6 +3684,9 @@
       <c r="F143" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G143" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
@@ -3282,6 +3707,9 @@
       <c r="F144" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G144" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
@@ -3302,6 +3730,9 @@
       <c r="F145" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G145" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
@@ -3322,6 +3753,9 @@
       <c r="F146" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G146" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
@@ -3342,6 +3776,9 @@
       <c r="F147" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G147" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
@@ -3362,6 +3799,9 @@
       <c r="F148" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G148" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
@@ -3382,6 +3822,9 @@
       <c r="F149" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G149" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
@@ -3402,6 +3845,9 @@
       <c r="F150" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G150" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
@@ -3422,6 +3868,9 @@
       <c r="F151" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G151" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
@@ -3442,6 +3891,9 @@
       <c r="F152" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G152" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
@@ -3462,6 +3914,9 @@
       <c r="F153" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G153" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
@@ -3482,6 +3937,9 @@
       <c r="F154" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G154" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
@@ -3502,6 +3960,9 @@
       <c r="F155" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G155" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
@@ -3522,6 +3983,9 @@
       <c r="F156" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G156" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
@@ -3542,6 +4006,9 @@
       <c r="F157" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G157" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
@@ -3562,6 +4029,9 @@
       <c r="F158" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G158" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
@@ -3582,6 +4052,9 @@
       <c r="F159" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G159" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
@@ -3602,6 +4075,9 @@
       <c r="F160" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G160" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
@@ -3622,6 +4098,9 @@
       <c r="F161" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G161" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
@@ -3642,6 +4121,9 @@
       <c r="F162" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G162" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
@@ -3662,6 +4144,9 @@
       <c r="F163" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G163" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
@@ -3682,6 +4167,9 @@
       <c r="F164" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G164" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
@@ -3702,6 +4190,9 @@
       <c r="F165" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G165" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
@@ -3722,6 +4213,9 @@
       <c r="F166" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G166" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
@@ -3742,6 +4236,9 @@
       <c r="F167" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G167" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
@@ -3762,6 +4259,9 @@
       <c r="F168" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G168" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
@@ -3782,6 +4282,9 @@
       <c r="F169" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G169" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
@@ -3802,6 +4305,9 @@
       <c r="F170" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G170" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
@@ -3822,6 +4328,9 @@
       <c r="F171" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G171" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
@@ -3842,6 +4351,9 @@
       <c r="F172" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G172" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
@@ -3862,6 +4374,9 @@
       <c r="F173" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G173" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
@@ -3882,6 +4397,9 @@
       <c r="F174" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G174" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
@@ -3902,6 +4420,9 @@
       <c r="F175" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G175" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
@@ -3922,6 +4443,9 @@
       <c r="F176" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G176" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
@@ -3942,6 +4466,9 @@
       <c r="F177" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G177" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
@@ -3962,6 +4489,9 @@
       <c r="F178" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G178" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
@@ -3982,6 +4512,9 @@
       <c r="F179" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G179" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
@@ -4002,6 +4535,9 @@
       <c r="F180" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G180" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
@@ -4022,6 +4558,9 @@
       <c r="F181" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G181" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
@@ -4042,6 +4581,9 @@
       <c r="F182" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G182" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
@@ -4062,6 +4604,9 @@
       <c r="F183" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G183" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
@@ -4082,6 +4627,9 @@
       <c r="F184" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G184" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
@@ -4102,6 +4650,9 @@
       <c r="F185" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G185" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
@@ -4122,6 +4673,9 @@
       <c r="F186" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G186" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
@@ -4142,6 +4696,9 @@
       <c r="F187" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G187" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
@@ -4162,6 +4719,9 @@
       <c r="F188" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G188" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
@@ -4182,6 +4742,9 @@
       <c r="F189" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G189" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
@@ -4202,6 +4765,9 @@
       <c r="F190" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G190" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
@@ -4222,6 +4788,9 @@
       <c r="F191" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G191" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
@@ -4242,6 +4811,9 @@
       <c r="F192" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G192" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
@@ -4262,6 +4834,9 @@
       <c r="F193" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G193" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
@@ -4282,6 +4857,9 @@
       <c r="F194" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G194" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
@@ -4302,6 +4880,9 @@
       <c r="F195" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G195" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
@@ -4322,6 +4903,9 @@
       <c r="F196" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G196" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
@@ -4342,6 +4926,9 @@
       <c r="F197" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G197" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
@@ -4362,6 +4949,9 @@
       <c r="F198" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G198" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
@@ -4382,6 +4972,9 @@
       <c r="F199" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G199" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
@@ -4402,6 +4995,9 @@
       <c r="F200" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G200" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
@@ -4422,6 +5018,9 @@
       <c r="F201" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G201" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
@@ -4442,6 +5041,9 @@
       <c r="F202" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G202" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
@@ -4462,6 +5064,9 @@
       <c r="F203" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G203" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
@@ -4482,6 +5087,9 @@
       <c r="F204" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G204" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
@@ -4502,6 +5110,9 @@
       <c r="F205" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G205" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
@@ -4522,6 +5133,9 @@
       <c r="F206" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G206" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
@@ -4542,6 +5156,9 @@
       <c r="F207" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G207" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
@@ -4562,6 +5179,9 @@
       <c r="F208" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G208" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
@@ -4582,6 +5202,9 @@
       <c r="F209" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G209" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
@@ -4602,6 +5225,9 @@
       <c r="F210" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G210" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
@@ -4622,6 +5248,9 @@
       <c r="F211" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G211" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
@@ -4642,6 +5271,9 @@
       <c r="F212" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G212" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
@@ -4662,6 +5294,9 @@
       <c r="F213" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G213" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
@@ -4682,6 +5317,9 @@
       <c r="F214" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G214" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
@@ -4702,6 +5340,9 @@
       <c r="F215" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G215" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
@@ -4722,6 +5363,9 @@
       <c r="F216" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G216" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
@@ -4742,6 +5386,9 @@
       <c r="F217" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G217" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
@@ -4762,6 +5409,9 @@
       <c r="F218" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G218" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
@@ -4782,6 +5432,9 @@
       <c r="F219" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G219" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
@@ -4802,6 +5455,9 @@
       <c r="F220" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G220" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
@@ -4822,6 +5478,9 @@
       <c r="F221" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G221" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
@@ -4842,6 +5501,9 @@
       <c r="F222" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G222" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
@@ -4862,6 +5524,9 @@
       <c r="F223" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G223" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
@@ -4882,6 +5547,9 @@
       <c r="F224" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G224" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
@@ -4902,6 +5570,9 @@
       <c r="F225" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G225" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
@@ -4922,6 +5593,9 @@
       <c r="F226" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G226" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
@@ -4942,6 +5616,9 @@
       <c r="F227" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G227" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
@@ -4962,6 +5639,9 @@
       <c r="F228" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G228" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
@@ -4982,6 +5662,9 @@
       <c r="F229" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G229" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
@@ -5002,6 +5685,9 @@
       <c r="F230" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G230" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
@@ -5022,6 +5708,9 @@
       <c r="F231" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G231" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
@@ -5042,6 +5731,9 @@
       <c r="F232" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G232" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
@@ -5062,6 +5754,9 @@
       <c r="F233" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G233" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
@@ -5082,6 +5777,9 @@
       <c r="F234" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G234" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
@@ -5102,6 +5800,9 @@
       <c r="F235" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G235" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
@@ -5122,6 +5823,9 @@
       <c r="F236" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G236" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
@@ -5142,6 +5846,9 @@
       <c r="F237" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G237" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
@@ -5162,6 +5869,9 @@
       <c r="F238" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G238" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
@@ -5182,6 +5892,9 @@
       <c r="F239" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G239" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
@@ -5202,6 +5915,9 @@
       <c r="F240" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G240" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
@@ -5222,6 +5938,9 @@
       <c r="F241" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G241" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
@@ -5242,6 +5961,9 @@
       <c r="F242" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G242" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
@@ -5262,6 +5984,9 @@
       <c r="F243" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G243" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
@@ -5282,6 +6007,9 @@
       <c r="F244" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G244" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
@@ -5302,6 +6030,9 @@
       <c r="F245" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G245" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
@@ -5322,6 +6053,9 @@
       <c r="F246" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G246" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
@@ -5342,6 +6076,9 @@
       <c r="F247" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G247" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
@@ -5362,6 +6099,9 @@
       <c r="F248" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G248" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
@@ -5382,6 +6122,9 @@
       <c r="F249" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G249" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
@@ -5402,6 +6145,9 @@
       <c r="F250" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G250" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
@@ -5422,6 +6168,9 @@
       <c r="F251" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G251" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
@@ -5442,6 +6191,9 @@
       <c r="F252" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G252" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
@@ -5462,6 +6214,9 @@
       <c r="F253" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G253" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
@@ -5482,6 +6237,9 @@
       <c r="F254" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G254" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
@@ -5502,6 +6260,9 @@
       <c r="F255" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G255" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
@@ -5522,6 +6283,9 @@
       <c r="F256" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G256" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
@@ -5542,6 +6306,9 @@
       <c r="F257" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G257" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
@@ -5562,6 +6329,9 @@
       <c r="F258" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G258" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
@@ -5582,6 +6352,9 @@
       <c r="F259" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G259" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
@@ -5602,6 +6375,9 @@
       <c r="F260" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G260" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
@@ -5622,6 +6398,9 @@
       <c r="F261" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G261" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
@@ -5642,6 +6421,9 @@
       <c r="F262" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G262" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
@@ -5662,6 +6444,9 @@
       <c r="F263" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G263" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
@@ -5682,6 +6467,9 @@
       <c r="F264" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G264" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
@@ -5702,6 +6490,9 @@
       <c r="F265" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G265" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
@@ -5722,6 +6513,9 @@
       <c r="F266" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G266" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
@@ -5742,6 +6536,9 @@
       <c r="F267" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G267" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
@@ -5762,6 +6559,9 @@
       <c r="F268" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G268" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
@@ -5782,6 +6582,9 @@
       <c r="F269" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G269" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
@@ -5802,6 +6605,9 @@
       <c r="F270" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G270" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
@@ -5822,6 +6628,9 @@
       <c r="F271" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G271" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
@@ -5842,6 +6651,9 @@
       <c r="F272" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G272" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
@@ -5862,6 +6674,9 @@
       <c r="F273" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G273" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
@@ -5882,6 +6697,9 @@
       <c r="F274" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G274" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
@@ -5902,6 +6720,9 @@
       <c r="F275" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G275" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
@@ -5922,6 +6743,9 @@
       <c r="F276" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G276" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
@@ -5942,6 +6766,9 @@
       <c r="F277" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G277" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
@@ -5962,6 +6789,9 @@
       <c r="F278" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G278" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
@@ -5982,6 +6812,9 @@
       <c r="F279" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G279" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
@@ -6002,6 +6835,9 @@
       <c r="F280" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G280" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
@@ -6022,6 +6858,9 @@
       <c r="F281" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G281" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
@@ -6042,6 +6881,9 @@
       <c r="F282" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G282" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
@@ -6062,6 +6904,9 @@
       <c r="F283" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G283" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
@@ -6082,6 +6927,9 @@
       <c r="F284" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G284" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
@@ -6102,6 +6950,9 @@
       <c r="F285" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G285" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
@@ -6122,6 +6973,9 @@
       <c r="F286" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G286" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
@@ -6142,6 +6996,9 @@
       <c r="F287" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G287" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
@@ -6162,6 +7019,9 @@
       <c r="F288" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G288" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
@@ -6182,6 +7042,9 @@
       <c r="F289" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G289" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
@@ -6202,6 +7065,9 @@
       <c r="F290" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G290" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
@@ -6222,6 +7088,9 @@
       <c r="F291" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G291" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
@@ -6242,6 +7111,9 @@
       <c r="F292" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G292" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
@@ -6262,6 +7134,9 @@
       <c r="F293" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G293" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
@@ -6282,6 +7157,9 @@
       <c r="F294" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G294" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
@@ -6302,6 +7180,9 @@
       <c r="F295" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G295" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
@@ -6322,6 +7203,9 @@
       <c r="F296" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G296" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
@@ -6342,6 +7226,9 @@
       <c r="F297" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G297" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
@@ -6362,6 +7249,9 @@
       <c r="F298" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G298" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
@@ -6382,6 +7272,9 @@
       <c r="F299" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G299" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
@@ -6402,6 +7295,9 @@
       <c r="F300" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G300" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
@@ -6422,6 +7318,9 @@
       <c r="F301" t="str">
         <v>量词任务</v>
       </c>
+      <c r="G301" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
@@ -6442,6 +7341,9 @@
       <c r="F302" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G302" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
@@ -6462,6 +7364,9 @@
       <c r="F303" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G303" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
@@ -6482,6 +7387,9 @@
       <c r="F304" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G304" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
@@ -6502,6 +7410,9 @@
       <c r="F305" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G305" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
@@ -6522,6 +7433,9 @@
       <c r="F306" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G306" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
@@ -6542,6 +7456,9 @@
       <c r="F307" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G307" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
@@ -6562,6 +7479,9 @@
       <c r="F308" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G308" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
@@ -6582,6 +7502,9 @@
       <c r="F309" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G309" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
@@ -6602,6 +7525,9 @@
       <c r="F310" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G310" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
@@ -6622,6 +7548,9 @@
       <c r="F311" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G311" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
@@ -6642,6 +7571,9 @@
       <c r="F312" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G312" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
@@ -6662,6 +7594,9 @@
       <c r="F313" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G313" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
@@ -6682,6 +7617,9 @@
       <c r="F314" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G314" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
@@ -6702,6 +7640,9 @@
       <c r="F315" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G315" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
@@ -6722,6 +7663,9 @@
       <c r="F316" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G316" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
@@ -6742,6 +7686,9 @@
       <c r="F317" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G317" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
@@ -6762,6 +7709,9 @@
       <c r="F318" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G318" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
@@ -6782,6 +7732,9 @@
       <c r="F319" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G319" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
@@ -6802,6 +7755,9 @@
       <c r="F320" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G320" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
@@ -6822,6 +7778,9 @@
       <c r="F321" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G321" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
@@ -6842,6 +7801,9 @@
       <c r="F322" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G322" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
@@ -6862,6 +7824,9 @@
       <c r="F323" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G323" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
@@ -6882,6 +7847,9 @@
       <c r="F324" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G324" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
@@ -6902,6 +7870,9 @@
       <c r="F325" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G325" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
@@ -6922,6 +7893,9 @@
       <c r="F326" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G326" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
@@ -6942,6 +7916,9 @@
       <c r="F327" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G327" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
@@ -6962,6 +7939,9 @@
       <c r="F328" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G328" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
@@ -6982,6 +7962,9 @@
       <c r="F329" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G329" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
@@ -7002,6 +7985,9 @@
       <c r="F330" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G330" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
@@ -7022,6 +8008,9 @@
       <c r="F331" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G331" t="str">
+        <v>有生命性</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
@@ -7042,6 +8031,9 @@
       <c r="F332" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G332" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
@@ -7062,6 +8054,9 @@
       <c r="F333" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G333" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
@@ -7082,6 +8077,9 @@
       <c r="F334" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G334" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
@@ -7102,6 +8100,9 @@
       <c r="F335" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G335" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
@@ -7122,6 +8123,9 @@
       <c r="F336" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G336" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
@@ -7142,6 +8146,9 @@
       <c r="F337" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G337" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
@@ -7162,6 +8169,9 @@
       <c r="F338" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G338" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
@@ -7182,6 +8192,9 @@
       <c r="F339" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G339" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
@@ -7202,6 +8215,9 @@
       <c r="F340" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G340" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
@@ -7222,6 +8238,9 @@
       <c r="F341" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G341" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
@@ -7242,6 +8261,9 @@
       <c r="F342" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G342" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
@@ -7262,6 +8284,9 @@
       <c r="F343" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G343" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
@@ -7282,6 +8307,9 @@
       <c r="F344" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G344" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
@@ -7302,6 +8330,9 @@
       <c r="F345" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G345" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
@@ -7322,6 +8353,9 @@
       <c r="F346" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G346" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
@@ -7342,6 +8376,9 @@
       <c r="F347" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G347" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
@@ -7362,6 +8399,9 @@
       <c r="F348" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G348" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
@@ -7382,6 +8422,9 @@
       <c r="F349" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G349" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
@@ -7402,6 +8445,9 @@
       <c r="F350" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G350" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
@@ -7422,6 +8468,9 @@
       <c r="F351" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G351" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
@@ -7442,6 +8491,9 @@
       <c r="F352" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G352" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
@@ -7462,6 +8514,9 @@
       <c r="F353" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G353" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
@@ -7482,6 +8537,9 @@
       <c r="F354" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G354" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
@@ -7502,6 +8560,9 @@
       <c r="F355" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G355" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
@@ -7522,6 +8583,9 @@
       <c r="F356" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G356" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
@@ -7542,6 +8606,9 @@
       <c r="F357" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G357" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
@@ -7562,6 +8629,9 @@
       <c r="F358" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G358" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
@@ -7582,6 +8652,9 @@
       <c r="F359" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G359" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
@@ -7602,6 +8675,9 @@
       <c r="F360" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G360" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
@@ -7622,10 +8698,13 @@
       <c r="F361" t="str">
         <v>自由描述任务</v>
       </c>
+      <c r="G361" t="str">
+        <v>无生命性</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F361"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G361"/>
   </ignoredErrors>
 </worksheet>
 </file>